--- a/templates/SH_Project_Report_Template_v3.xlsx
+++ b/templates/SH_Project_Report_Template_v3.xlsx
@@ -1081,7 +1081,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A3" s="11" t="s">
+      <c r="A3" t="s">
         <v>14</v>
       </c>
     </row>

--- a/templates/SH_Project_Report_Template_v3.xlsx
+++ b/templates/SH_Project_Report_Template_v3.xlsx
@@ -18,7 +18,7 @@
     <sheet name="Dashboard" sheetId="3" r:id="rId3"/>
     <sheet name="Template Guide" sheetId="4" state="hidden" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1614,28 +1614,28 @@
     </row>
     <row r="6" spans="1:10" ht="21.75" customHeight="1">
       <c r="A6" s="7">
-        <f>COUNTA('Project Data'!$A$3:$A$10000)-COUNTBLANK('Project Data'!$A$3:$A$10000)</f>
-        <v>-9996</v>
+        <f>COUNTA('Project Data'!$A$3:$A$10000)</f>
+        <v/>
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="7">
         <f>COUNTIF(_Pivot!A2:A31,"?*")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="D6" s="7"/>
       <c r="E6" s="7">
         <f>COUNTIF('Project Data'!$E$3:$E$10000,"Interview")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="F6" s="7"/>
       <c r="G6" s="7">
         <f>COUNTIF('Project Data'!$E$3:$E$10000,"Offer")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H6" s="7"/>
       <c r="I6" s="7">
         <f>COUNTIF('Project Data'!$E$3:$E$10000,"Placed")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="J6" s="7"/>
     </row>
@@ -2107,7 +2107,7 @@
       <c r="H28" s="4"/>
       <c r="I28" s="16">
         <f>IF(F28="","",COUNTIF('Project Data'!$D$3:$D$10000,F28))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="J28" s="17" t="str">
         <f>IFERROR(I28/SUM(I28:I35),"")</f>
@@ -2138,7 +2138,7 @@
       <c r="H29" s="3"/>
       <c r="I29" s="20">
         <f>IF(F29="","",COUNTIF('Project Data'!$D$3:$D$10000,F29))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="J29" s="21" t="str">
         <f>IFERROR(I29/SUM(I28:I35),"")</f>
@@ -2169,7 +2169,7 @@
       <c r="H30" s="4"/>
       <c r="I30" s="16">
         <f>IF(F30="","",COUNTIF('Project Data'!$D$3:$D$10000,F30))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="J30" s="17" t="str">
         <f>IFERROR(I30/SUM(I28:I35),"")</f>
@@ -2200,7 +2200,7 @@
       <c r="H31" s="3"/>
       <c r="I31" s="20">
         <f>IF(F31="","",COUNTIF('Project Data'!$D$3:$D$10000,F31))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="J31" s="21" t="str">
         <f>IFERROR(I31/SUM(I28:I35),"")</f>
@@ -2231,7 +2231,7 @@
       <c r="H32" s="4"/>
       <c r="I32" s="16">
         <f>IF(F32="","",COUNTIF('Project Data'!$D$3:$D$10000,F32))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="J32" s="17" t="str">
         <f>IFERROR(I32/SUM(I28:I35),"")</f>
@@ -2262,7 +2262,7 @@
       <c r="H33" s="3"/>
       <c r="I33" s="20">
         <f>IF(F33="","",COUNTIF('Project Data'!$D$3:$D$10000,F33))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="J33" s="21" t="str">
         <f>IFERROR(I33/SUM(I28:I35),"")</f>
@@ -2293,7 +2293,7 @@
       <c r="H34" s="4"/>
       <c r="I34" s="16">
         <f>IF(F34="","",COUNTIF('Project Data'!$D$3:$D$10000,F34))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="J34" s="17" t="str">
         <f>IFERROR(I34/SUM(I28:I35),"")</f>
@@ -2324,7 +2324,7 @@
       <c r="H35" s="3"/>
       <c r="I35" s="20">
         <f>IF(F35="","",COUNTIF('Project Data'!$D$3:$D$10000,F35))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="J35" s="21" t="str">
         <f>IFERROR(I35/SUM(I28:I35),"")</f>
@@ -2462,12 +2462,12 @@
         <v>59</v>
       </c>
       <c r="B43" s="24">
-        <f>COUNTA('Project Data'!$A$3:$A$10000)-COUNTBLANK('Project Data'!$A$3:$A$10000)</f>
-        <v>-9996</v>
+        <f>COUNTA('Project Data'!$A$3:$A$10000)</f>
+        <v/>
       </c>
       <c r="C43" s="25">
         <f>IFERROR(SUM(C13:C42),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="D43" s="26"/>
     </row>
@@ -2500,11 +2500,11 @@
       </c>
       <c r="B47" s="16">
         <f>COUNTIF('Project Data'!$F$3:$F$10000,A47)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C47" s="17">
         <f>IFERROR(B47/SUM(B47:B50),0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="D47" s="18" t="str">
         <f>IFERROR(REPT("█",ROUND(C47*20,0)),"")</f>
@@ -2517,11 +2517,11 @@
       </c>
       <c r="B48" s="20">
         <f>COUNTIF('Project Data'!$F$3:$F$10000,A48)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C48" s="21">
         <f>IFERROR(B48/SUM(B47:B50),0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="D48" s="22" t="str">
         <f>IFERROR(REPT("█",ROUND(C48*20,0)),"")</f>
@@ -2534,11 +2534,11 @@
       </c>
       <c r="B49" s="16">
         <f>COUNTIF('Project Data'!$F$3:$F$10000,A49)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C49" s="17">
         <f>IFERROR(B49/SUM(B47:B50),0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="D49" s="18" t="str">
         <f>IFERROR(REPT("█",ROUND(C49*20,0)),"")</f>
@@ -2551,11 +2551,11 @@
       </c>
       <c r="B50" s="20">
         <f>COUNTIF('Project Data'!$F$3:$F$10000,A50)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C50" s="21">
         <f>IFERROR(B50/SUM(B47:B50),0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="D50" s="22" t="str">
         <f>IFERROR(REPT("█",ROUND(C50*20,0)),"")</f>

--- a/templates/SH_Project_Report_Template_v3.xlsx
+++ b/templates/SH_Project_Report_Template_v3.xlsx
@@ -18,7 +18,7 @@
     <sheet name="Dashboard" sheetId="3" r:id="rId3"/>
     <sheet name="Template Guide" sheetId="4" state="hidden" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1081,11 +1081,12 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A3" t="s">
+      <c r="A3" s="11" t="s">
         <v>14</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A2:G2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -1109,7 +1110,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="str">
-        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A1,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A1,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B2" t="str">
@@ -1123,7 +1124,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="str">
-        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A2,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A2,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B3" t="str">
@@ -1137,7 +1138,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="str">
-        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A3,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A3,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B4" t="str">
@@ -1151,7 +1152,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="str">
-        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A4,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A4,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B5" t="str">
@@ -1165,7 +1166,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="str">
-        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A5,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A5,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B6" t="str">
@@ -1179,7 +1180,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="str">
-        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A6,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A6,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B7" t="str">
@@ -1193,7 +1194,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="str">
-        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A7,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A7,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B8" t="str">
@@ -1207,7 +1208,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="str">
-        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A8,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A8,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B9" t="str">
@@ -1221,7 +1222,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="str">
-        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A9,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A9,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B10" t="str">
@@ -1235,7 +1236,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="str">
-        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A10,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A10,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B11" t="str">
@@ -1249,7 +1250,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="str">
-        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A11,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A11,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B12" t="str">
@@ -1263,7 +1264,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="str">
-        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A12,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A12,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B13" t="str">
@@ -1277,7 +1278,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="str">
-        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A13,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A13,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B14" t="str">
@@ -1291,7 +1292,7 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="str">
-        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A14,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A14,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B15" t="str">
@@ -1305,7 +1306,7 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="str">
-        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A15,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A15,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B16" t="str">
@@ -1319,7 +1320,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="str">
-        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A16,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A16,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B17" t="str">
@@ -1333,7 +1334,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="str">
-        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A17,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A17,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B18" t="str">
@@ -1347,7 +1348,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="str">
-        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A18,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A18,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B19" t="str">
@@ -1361,7 +1362,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="str">
-        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A19,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A19,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B20" t="str">
@@ -1375,7 +1376,7 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="str">
-        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A20,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A20,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B21" t="str">
@@ -1389,7 +1390,7 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="str">
-        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A21,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A21,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B22" t="str">
@@ -1403,7 +1404,7 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="str">
-        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A22,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A22,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B23" t="str">
@@ -1417,7 +1418,7 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="str">
-        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A23,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A23,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B24" t="str">
@@ -1431,7 +1432,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="str">
-        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A24,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A24,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B25" t="str">
@@ -1445,7 +1446,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="str">
-        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A25,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A25,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B26" t="str">
@@ -1459,7 +1460,7 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="str">
-        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A26,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A26,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B27" t="str">
@@ -1473,7 +1474,7 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="str">
-        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A27,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A27,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B28" t="str">
@@ -1487,7 +1488,7 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="str">
-        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A28,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A28,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B29" t="str">
@@ -1501,7 +1502,7 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="str">
-        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A29,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A29,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B30" t="str">
@@ -1515,7 +1516,7 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="str">
-        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A30,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A30,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B31" t="str">
@@ -1614,28 +1615,28 @@
     </row>
     <row r="6" spans="1:10" ht="21.75" customHeight="1">
       <c r="A6" s="7">
-        <f>COUNTA('Project Data'!$A$3:$A$10000)</f>
-        <v/>
+        <f>COUNTA('Project Data'!$A$3:$A$10000)-COUNTBLANK('Project Data'!$A$3:$A$10000)</f>
+        <v>-9996</v>
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="7">
         <f>COUNTIF(_Pivot!A2:A31,"?*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D6" s="7"/>
       <c r="E6" s="7">
         <f>COUNTIF('Project Data'!$E$3:$E$10000,"Interview")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F6" s="7"/>
       <c r="G6" s="7">
         <f>COUNTIF('Project Data'!$E$3:$E$10000,"Offer")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H6" s="7"/>
       <c r="I6" s="7">
         <f>COUNTIF('Project Data'!$E$3:$E$10000,"Placed")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J6" s="7"/>
     </row>
@@ -2107,7 +2108,7 @@
       <c r="H28" s="4"/>
       <c r="I28" s="16">
         <f>IF(F28="","",COUNTIF('Project Data'!$D$3:$D$10000,F28))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J28" s="17" t="str">
         <f>IFERROR(I28/SUM(I28:I35),"")</f>
@@ -2138,7 +2139,7 @@
       <c r="H29" s="3"/>
       <c r="I29" s="20">
         <f>IF(F29="","",COUNTIF('Project Data'!$D$3:$D$10000,F29))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J29" s="21" t="str">
         <f>IFERROR(I29/SUM(I28:I35),"")</f>
@@ -2169,7 +2170,7 @@
       <c r="H30" s="4"/>
       <c r="I30" s="16">
         <f>IF(F30="","",COUNTIF('Project Data'!$D$3:$D$10000,F30))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J30" s="17" t="str">
         <f>IFERROR(I30/SUM(I28:I35),"")</f>
@@ -2200,7 +2201,7 @@
       <c r="H31" s="3"/>
       <c r="I31" s="20">
         <f>IF(F31="","",COUNTIF('Project Data'!$D$3:$D$10000,F31))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J31" s="21" t="str">
         <f>IFERROR(I31/SUM(I28:I35),"")</f>
@@ -2231,7 +2232,7 @@
       <c r="H32" s="4"/>
       <c r="I32" s="16">
         <f>IF(F32="","",COUNTIF('Project Data'!$D$3:$D$10000,F32))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J32" s="17" t="str">
         <f>IFERROR(I32/SUM(I28:I35),"")</f>
@@ -2262,7 +2263,7 @@
       <c r="H33" s="3"/>
       <c r="I33" s="20">
         <f>IF(F33="","",COUNTIF('Project Data'!$D$3:$D$10000,F33))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J33" s="21" t="str">
         <f>IFERROR(I33/SUM(I28:I35),"")</f>
@@ -2293,7 +2294,7 @@
       <c r="H34" s="4"/>
       <c r="I34" s="16">
         <f>IF(F34="","",COUNTIF('Project Data'!$D$3:$D$10000,F34))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J34" s="17" t="str">
         <f>IFERROR(I34/SUM(I28:I35),"")</f>
@@ -2324,7 +2325,7 @@
       <c r="H35" s="3"/>
       <c r="I35" s="20">
         <f>IF(F35="","",COUNTIF('Project Data'!$D$3:$D$10000,F35))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J35" s="21" t="str">
         <f>IFERROR(I35/SUM(I28:I35),"")</f>
@@ -2462,12 +2463,12 @@
         <v>59</v>
       </c>
       <c r="B43" s="24">
-        <f>COUNTA('Project Data'!$A$3:$A$10000)</f>
-        <v/>
+        <f>COUNTA('Project Data'!$A$3:$A$10000)-COUNTBLANK('Project Data'!$A$3:$A$10000)</f>
+        <v>-9996</v>
       </c>
       <c r="C43" s="25">
         <f>IFERROR(SUM(C13:C42),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D43" s="26"/>
     </row>
@@ -2500,11 +2501,11 @@
       </c>
       <c r="B47" s="16">
         <f>COUNTIF('Project Data'!$F$3:$F$10000,A47)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C47" s="17">
         <f>IFERROR(B47/SUM(B47:B50),0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D47" s="18" t="str">
         <f>IFERROR(REPT("█",ROUND(C47*20,0)),"")</f>
@@ -2517,11 +2518,11 @@
       </c>
       <c r="B48" s="20">
         <f>COUNTIF('Project Data'!$F$3:$F$10000,A48)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C48" s="21">
         <f>IFERROR(B48/SUM(B47:B50),0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D48" s="22" t="str">
         <f>IFERROR(REPT("█",ROUND(C48*20,0)),"")</f>
@@ -2534,11 +2535,11 @@
       </c>
       <c r="B49" s="16">
         <f>COUNTIF('Project Data'!$F$3:$F$10000,A49)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C49" s="17">
         <f>IFERROR(B49/SUM(B47:B50),0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D49" s="18" t="str">
         <f>IFERROR(REPT("█",ROUND(C49*20,0)),"")</f>
@@ -2551,11 +2552,11 @@
       </c>
       <c r="B50" s="20">
         <f>COUNTIF('Project Data'!$F$3:$F$10000,A50)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C50" s="21">
         <f>IFERROR(B50/SUM(B47:B50),0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D50" s="22" t="str">
         <f>IFERROR(REPT("█",ROUND(C50*20,0)),"")</f>

--- a/templates/SH_Project_Report_Template_v3.xlsx
+++ b/templates/SH_Project_Report_Template_v3.xlsx
@@ -1086,7 +1086,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:G2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -1110,7 +1109,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="str">
-        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A1,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A1,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B2" t="str">
@@ -1124,7 +1123,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="str">
-        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A2,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A2,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B3" t="str">
@@ -1138,7 +1137,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="str">
-        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A3,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A3,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B4" t="str">
@@ -1152,7 +1151,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="str">
-        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A4,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A4,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B5" t="str">
@@ -1166,7 +1165,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="str">
-        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A5,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A5,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B6" t="str">
@@ -1180,7 +1179,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="str">
-        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A6,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A6,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B7" t="str">
@@ -1194,7 +1193,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="str">
-        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A7,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A7,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B8" t="str">
@@ -1208,7 +1207,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="str">
-        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A8,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A8,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B9" t="str">
@@ -1222,7 +1221,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="str">
-        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A9,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A9,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B10" t="str">
@@ -1236,7 +1235,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="str">
-        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A10,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A10,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B11" t="str">
@@ -1250,7 +1249,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="str">
-        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A11,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A11,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B12" t="str">
@@ -1264,7 +1263,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="str">
-        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A12,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A12,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B13" t="str">
@@ -1278,7 +1277,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="str">
-        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A13,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A13,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B14" t="str">
@@ -1292,7 +1291,7 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="str">
-        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A14,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A14,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B15" t="str">
@@ -1306,7 +1305,7 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="str">
-        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A15,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A15,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B16" t="str">
@@ -1320,7 +1319,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="str">
-        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A16,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A16,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B17" t="str">
@@ -1334,7 +1333,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="str">
-        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A17,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A17,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B18" t="str">
@@ -1348,7 +1347,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="str">
-        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A18,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A18,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B19" t="str">
@@ -1362,7 +1361,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="str">
-        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A19,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A19,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B20" t="str">
@@ -1376,7 +1375,7 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="str">
-        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A20,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A20,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B21" t="str">
@@ -1390,7 +1389,7 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="str">
-        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A21,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A21,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B22" t="str">
@@ -1404,7 +1403,7 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="str">
-        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A22,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A22,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B23" t="str">
@@ -1418,7 +1417,7 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="str">
-        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A23,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A23,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B24" t="str">
@@ -1432,7 +1431,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="str">
-        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A24,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A24,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B25" t="str">
@@ -1446,7 +1445,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="str">
-        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A25,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A25,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B26" t="str">
@@ -1460,7 +1459,7 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="str">
-        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A26,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A26,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B27" t="str">
@@ -1474,7 +1473,7 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="str">
-        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A27,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A27,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B28" t="str">
@@ -1488,7 +1487,7 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="str">
-        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A28,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A28,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B29" t="str">
@@ -1502,7 +1501,7 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="str">
-        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A29,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A29,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B30" t="str">
@@ -1516,7 +1515,7 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="str">
-        <f t="array">IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A30,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A30,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
         <v/>
       </c>
       <c r="B31" t="str">
@@ -1615,27 +1614,27 @@
     </row>
     <row r="6" spans="1:10" ht="21.75" customHeight="1">
       <c r="A6" s="7">
-        <f>COUNTA('Project Data'!$A$3:$A$10000)-COUNTBLANK('Project Data'!$A$3:$A$10000)</f>
-        <v>-9996</v>
+        <f>COUNTA('Project Data'!$A$3:$A$10000)</f>
+        <v>0</v>
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="7">
-        <f>COUNTIF(_Pivot!A2:A31,"?*")</f>
+        <f>COUNTA(_Pivot!A2:A31)</f>
         <v>0</v>
       </c>
       <c r="D6" s="7"/>
       <c r="E6" s="7">
-        <f>COUNTIF('Project Data'!$E$3:$E$10000,"Interview")</f>
+        <f>COUNTIF('Project Data'!$E$3:$E$10000,"*Interview*")</f>
         <v>0</v>
       </c>
       <c r="F6" s="7"/>
       <c r="G6" s="7">
-        <f>COUNTIF('Project Data'!$E$3:$E$10000,"Offer")</f>
+        <f>COUNTIF('Project Data'!$E$3:$E$10000,"*Offer*")</f>
         <v>0</v>
       </c>
       <c r="H6" s="7"/>
       <c r="I6" s="7">
-        <f>COUNTIF('Project Data'!$E$3:$E$10000,"Placed")</f>
+        <f>COUNTIF('Project Data'!$E$3:$E$10000,"*Placed*")</f>
         <v>0</v>
       </c>
       <c r="J6" s="7"/>
@@ -2463,8 +2462,8 @@
         <v>59</v>
       </c>
       <c r="B43" s="24">
-        <f>COUNTA('Project Data'!$A$3:$A$10000)-COUNTBLANK('Project Data'!$A$3:$A$10000)</f>
-        <v>-9996</v>
+        <f>COUNTA('Project Data'!$A$3:$A$10000)</f>
+        <v>0</v>
       </c>
       <c r="C43" s="25">
         <f>IFERROR(SUM(C13:C42),"")</f>
@@ -2500,7 +2499,7 @@
         <v>62</v>
       </c>
       <c r="B47" s="16">
-        <f>COUNTIF('Project Data'!$F$3:$F$10000,A47)</f>
+        <f>COUNTIF('Project Data'!$F$3:$F$10000,"Male")</f>
         <v>0</v>
       </c>
       <c r="C47" s="17">
@@ -2517,7 +2516,7 @@
         <v>63</v>
       </c>
       <c r="B48" s="20">
-        <f>COUNTIF('Project Data'!$F$3:$F$10000,A48)</f>
+        <f>COUNTIF('Project Data'!$F$3:$F$10000,"Female")</f>
         <v>0</v>
       </c>
       <c r="C48" s="21">
@@ -2533,8 +2532,8 @@
       <c r="A49" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="B49" s="16">
-        <f>COUNTIF('Project Data'!$F$3:$F$10000,A49)</f>
+      <c r="B49" s="20">
+        <f>COUNTIF('Project Data'!$F$3:$F$10000,"Non-Binary*")</f>
         <v>0</v>
       </c>
       <c r="C49" s="17">

--- a/templates/SH_Project_Report_Template_v3.xlsx
+++ b/templates/SH_Project_Report_Template_v3.xlsx
@@ -1086,6 +1086,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A2:G2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
